--- a/src/files/archivo_actualizado.xlsx
+++ b/src/files/archivo_actualizado.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>El Sr. (a) ___________________________ identificado con cédula de ciudadanía No:_________________, manifiesto que estoy informado de los riesgos contra los que me protegen estos elementos que estoy recibiendo, de las actividades u ocasiones en que debo utilizarlos, de la forma correcta para su uso y sus limitaciones. Me comprometo a hacer buen uso de los EPP entregados, a su vez conozco y acpeto ser  responsable por la pérdida y daños ocasionados por el mal uso o descuido, de ser así autorizo a la empresa para que haga el descuento de mi salario, prestaciones sociales y demás emolumentos laborales, del costo de los EPP. De igual forma para efectos de control de la dotación, devolveré la anteriormente entregada al momento de recibir la del siguiente período. La no utilización de los elementos de protección personal y el descuido de los mismos acarrea sanciones administrativas y/o disciplinarias.</t>
+    <t>El Sr. (a) AGUILAR BRAVO JAQUELINE MONTSERRAT identificado con cédula de ciudadanía No: 11056, manifiesto que estoy informado de los riesgos contra los que me protegen estos elementos que estoy recibiendo, de las actividades u ocasiones en que debo utilizarlos, de la forma correcta para su uso y sus limitaciones. Me comprometo a hacer buen uso de los EPP entregados, a su vez conozco y acpeto ser  responsable por la pérdida y daños ocasionados por el mal uso o descuido, de ser así autorizo a la empresa para que haga el descuento de mi salario, prestaciones sociales y demás emolumentos laborales, del costo de los EPP. De igual forma para efectos de control de la dotación, devolveré la anteriormente entregada al momento de recibir la del siguiente período. La no utilización de los elementos de protección personal y el descuido de los mismos acarrea sanciones administrativas y/o disciplinarias.</t>
   </si>
 </sst>
 </file>

--- a/src/files/archivo_actualizado.xlsx
+++ b/src/files/archivo_actualizado.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
   <si>
     <t>NOMBRE DEL EMPLEADO: AGUILAR BRAVO JAQUELINE MONTSERRAT</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>BOTA DE SEGURIDAD</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -447,12 +453,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6858000" cy="1524000"/>
+    <xdr:ext cx="952500" cy="238125"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -468,6 +474,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6858000" cy="1524000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -894,9 +939,13 @@
       <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
@@ -908,7 +957,7 @@
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -917,7 +966,7 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -954,7 +1003,7 @@
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -963,7 +1012,7 @@
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -972,7 +1021,7 @@
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -981,7 +1030,7 @@
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -997,7 +1046,7 @@
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1006,7 +1055,7 @@
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1015,7 +1064,7 @@
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1031,7 +1080,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1040,7 +1089,7 @@
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -1049,7 +1098,7 @@
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -1058,7 +1107,7 @@
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -1088,7 +1137,7 @@
     </row>
     <row r="34" ht="36.75" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
